--- a/Kwartaalrapportage/VISMA/Q1 2026 Tech.xlsx
+++ b/Kwartaalrapportage/VISMA/Q1 2026 Tech.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tgf-my.sharepoint.com/personal/tom_meijer_theglobalfund_org/Documents/Documents/Temp/Blueplates/Rapportage/Q1 2026/VISMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_31CB829202D80C5747D2C041DE2459E2EF6E276A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A6B5C30-9DC9-6947-99FC-625ACD6F8C66}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_31CB829202D80C5747D2C041DE2459E2EF6E276A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A69F2C8-38D9-0846-A9F2-2E83F748E299}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
   <si>
     <t>Organisatie:</t>
   </si>
@@ -273,9 +273,6 @@
   </si>
   <si>
     <t>Te betalen vakantiegelden</t>
-  </si>
-  <si>
-    <t>800100</t>
   </si>
   <si>
     <t>Omzet algemeen 21%</t>
@@ -1786,14 +1783,14 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="12" x14ac:dyDescent="0.15">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="5">
+        <v>800100</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="D35" s="11">
         <v>0</v>
@@ -1810,13 +1807,13 @@
     </row>
     <row r="36" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="D36" s="11">
         <v>0</v>
@@ -1833,13 +1830,13 @@
     </row>
     <row r="37" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="D37" s="11">
         <v>0</v>
@@ -1856,13 +1853,13 @@
     </row>
     <row r="38" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="D38" s="11">
         <v>0</v>
@@ -1879,13 +1876,13 @@
     </row>
     <row r="39" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="D39" s="11">
         <v>0</v>
@@ -1902,13 +1899,13 @@
     </row>
     <row r="40" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="D40" s="11">
         <v>0</v>
@@ -1925,13 +1922,13 @@
     </row>
     <row r="41" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="D41" s="11">
         <v>0</v>
@@ -1948,13 +1945,13 @@
     </row>
     <row r="42" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="D42" s="11">
         <v>0</v>
@@ -1971,13 +1968,13 @@
     </row>
     <row r="43" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="D43" s="11">
         <v>0</v>
@@ -1994,13 +1991,13 @@
     </row>
     <row r="44" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D44" s="11">
         <v>0</v>
@@ -2017,13 +2014,13 @@
     </row>
     <row r="45" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="D45" s="11">
         <v>0</v>
@@ -2040,13 +2037,13 @@
     </row>
     <row r="46" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="D46" s="11">
         <v>0</v>
@@ -2063,13 +2060,13 @@
     </row>
     <row r="47" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A47" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="D47" s="11">
         <v>0</v>
@@ -2086,13 +2083,13 @@
     </row>
     <row r="48" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A48" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="D48" s="11">
         <v>0</v>
@@ -2109,13 +2106,13 @@
     </row>
     <row r="49" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A49" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="D49" s="11">
         <v>0</v>
@@ -2132,13 +2129,13 @@
     </row>
     <row r="50" spans="1:7" ht="12" x14ac:dyDescent="0.15">
       <c r="A50" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="D50" s="11">
         <v>0</v>
@@ -2157,7 +2154,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D51" s="13">
         <v>-6.3664629124105001E-12</v>

--- a/Kwartaalrapportage/VISMA/Q1 2026 Tech.xlsx
+++ b/Kwartaalrapportage/VISMA/Q1 2026 Tech.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tgf-my.sharepoint.com/personal/tom_meijer_theglobalfund_org/Documents/Documents/Temp/Blueplates/Rapportage/Q1 2026/VISMA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommeijer/Git/Kwartaalrapportage/VISMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_31CB829202D80C5747D2C041DE2459E2EF6E276A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A69F2C8-38D9-0846-A9F2-2E83F748E299}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A254CCF6-648E-4F4E-B6F3-CB6819174C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -385,7 +385,7 @@
     <numFmt numFmtId="164" formatCode="d\-m\-yyyy\ hh:mm"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\-#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -423,8 +423,14 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +458,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -623,7 +635,7 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="28">
       <alignment horizontal="left" vertical="top"/>
@@ -664,6 +676,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="43" applyFont="1" applyFill="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1014,7 +1029,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -1024,7 +1039,7 @@
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -1039,7 +1054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1075,7 @@
         <v>46134.252230421102</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1081,7 +1096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1092,7 +1107,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1101,7 +1116,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1124,7 +1139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
@@ -1137,24 +1152,25 @@
       <c r="D7" s="11">
         <v>6578.82</v>
       </c>
-      <c r="E7" s="11">
-        <v>0</v>
+      <c r="E7" s="16">
+        <v>5011.34</v>
       </c>
       <c r="F7" s="11">
         <v>0</v>
       </c>
-      <c r="G7" s="11">
-        <v>6578.82</v>
+      <c r="G7" s="16">
+        <f>D7+E7-F7</f>
+        <v>11590.16</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>24</v>
       </c>
       <c r="K7" s="15">
         <f>SUMIFS(G:G,B:B,"A")</f>
-        <v>71705.76999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+        <v>76717.109999999986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>25</v>
       </c>
@@ -1184,7 +1200,7 @@
         <v>-102962.75999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -1207,7 +1223,7 @@
         <v>38868</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -1230,7 +1246,7 @@
         <v>-7068.08</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
@@ -1253,7 +1269,7 @@
         <v>2220.02</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>33</v>
       </c>
@@ -1276,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>35</v>
       </c>
@@ -1299,7 +1315,7 @@
         <v>40820.53</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
@@ -1322,7 +1338,7 @@
         <v>67.34</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
@@ -1345,7 +1361,7 @@
         <v>-1479.71</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="12" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
@@ -1368,7 +1384,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
@@ -1391,7 +1407,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>46</v>
       </c>
@@ -1414,7 +1430,7 @@
         <v>126011.32</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>48</v>
       </c>
@@ -1437,7 +1453,7 @@
         <v>203713.75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
         <v>50</v>
       </c>
@@ -1460,7 +1476,7 @@
         <v>-46195.68</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
@@ -1483,7 +1499,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>54</v>
       </c>
@@ -1506,7 +1522,7 @@
         <v>-250</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>56</v>
       </c>
@@ -1529,7 +1545,7 @@
         <v>-174774.29</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>58</v>
       </c>
@@ -1552,7 +1568,7 @@
         <v>-135567.91</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>60</v>
       </c>
@@ -1575,7 +1591,7 @@
         <v>-71659.710000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
         <v>62</v>
       </c>
@@ -1598,7 +1614,7 @@
         <v>-19084.009999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>64</v>
       </c>
@@ -1621,7 +1637,7 @@
         <v>16329.55</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>66</v>
       </c>
@@ -1644,7 +1660,7 @@
         <v>-1032.18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>68</v>
       </c>
@@ -1667,7 +1683,7 @@
         <v>1582.08</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
         <v>70</v>
       </c>
@@ -1690,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
         <v>72</v>
       </c>
@@ -1713,7 +1729,7 @@
         <v>-43084.22</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="5" t="s">
         <v>74</v>
       </c>
@@ -1736,7 +1752,7 @@
         <v>47925.38</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>76</v>
       </c>
@@ -1759,7 +1775,7 @@
         <v>-428.4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
         <v>78</v>
       </c>
@@ -1782,7 +1798,7 @@
         <v>-6436.44</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="5">
         <v>800100</v>
       </c>
@@ -1805,7 +1821,7 @@
         <v>-4916.26</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
         <v>82</v>
       </c>
@@ -1828,7 +1844,7 @@
         <v>19402.12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
         <v>85</v>
       </c>
@@ -1851,7 +1867,7 @@
         <v>-390.78</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
         <v>87</v>
       </c>
@@ -1874,7 +1890,7 @@
         <v>3981.12</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
         <v>89</v>
       </c>
@@ -1897,7 +1913,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>91</v>
       </c>
@@ -1920,7 +1936,7 @@
         <v>4387.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>93</v>
       </c>
@@ -1943,7 +1959,7 @@
         <v>14.04</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
         <v>95</v>
       </c>
@@ -1966,7 +1982,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
         <v>97</v>
       </c>
@@ -1989,7 +2005,7 @@
         <v>748.31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
         <v>99</v>
       </c>
@@ -2002,17 +2018,17 @@
       <c r="D44" s="11">
         <v>0</v>
       </c>
-      <c r="E44" s="11">
-        <v>2141.34</v>
+      <c r="E44" s="16">
+        <v>0</v>
       </c>
       <c r="F44" s="11">
         <v>0</v>
       </c>
-      <c r="G44" s="11">
-        <v>2141.34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+      <c r="G44" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
         <v>101</v>
       </c>
@@ -2035,7 +2051,7 @@
         <v>625.84</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
         <v>103</v>
       </c>
@@ -2058,7 +2074,7 @@
         <v>561.03</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="5" t="s">
         <v>105</v>
       </c>
@@ -2081,7 +2097,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="5" t="s">
         <v>107</v>
       </c>
@@ -2104,7 +2120,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="5" t="s">
         <v>109</v>
       </c>
@@ -2127,7 +2143,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="5" t="s">
         <v>111</v>
       </c>
@@ -2140,17 +2156,19 @@
       <c r="D50" s="11">
         <v>0</v>
       </c>
-      <c r="E50" s="11">
-        <v>3821.96</v>
+      <c r="E50" s="16">
+        <f>3821.96-2870</f>
+        <v>951.96</v>
       </c>
       <c r="F50" s="11">
         <v>0</v>
       </c>
-      <c r="G50" s="11">
-        <v>3821.96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="12" x14ac:dyDescent="0.15">
+      <c r="G50" s="16">
+        <f>E50</f>
+        <v>951.96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="12" t="s">
@@ -2171,6 +2189,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
